--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -1129,7 +1129,11 @@
           <t>FIRF GERAES</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>BRHAPVDBS014</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1633,7 +1637,11 @@
           <t>BMG SEG</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>BRBMEBLFI8V4</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -2315,7 +2323,11 @@
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2408,7 +2420,11 @@
           <t>BORDEAUX INFRA</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2435,7 +2451,11 @@
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2590,7 +2610,11 @@
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>BRBPACLFIVQ4</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -614,7 +614,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,25 +694,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PARANA BANCO S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CDB3253PPYA</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>46091</v>
+        <v>46454</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BRPRBCC059P8</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -808,11 +808,7 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -835,7 +831,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -843,7 +839,11 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -874,11 +874,7 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -888,28 +884,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>PARANA BANCO S.A.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CDB424EERW3</t>
+          <t>CDB3253PPYA</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>46146</v>
+        <v>46091</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>BRBVKWC00WA0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>BRPRBCC059P8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BBRASIL FIM</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -950,32 +950,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BANCO INTER SA</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CDB7257QUDF</t>
+          <t>CDB424EERW3</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>46213</v>
+        <v>46146</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>BBRASIL FIM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BRBIDIC002H4</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>613312-CDB</t>
-        </is>
-      </c>
+          <t>BRBVKWC00WA0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -990,7 +986,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CDB7257QUDG</t>
+          <t>CDB7257QUDF</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -998,7 +994,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1006,7 +1002,11 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>613312-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CDB7257QUDH</t>
+          <t>CDB7257QUDG</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CDB7257QUDI</t>
+          <t>CDB7257QUDH</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1068,11 +1068,7 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>613315-CDB</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1082,56 +1078,60 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>BANCO INTER SA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CDB925CDN0L</t>
+          <t>CDB7257QUDI</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>46013</v>
+        <v>46213</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BRBVKWC01543</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>BRBIDIC002H4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>613315-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB925CDN0L</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46213</v>
+        <v>46013</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
+          <t>BRBVKWC01543</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1165,11 +1165,7 @@
           <t>BRHAPVDBS014</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>362409-HAP</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1179,28 +1175,32 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>47196</v>
+        <v>46213</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>BRHAPVDBS014</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>362409-HAP</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1324,42 +1324,42 @@
           <t>BRKLBNDBS004</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>353017-KLB</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>46083</v>
+        <v>47196</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>353017-KLB</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1374,20 +1374,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LF0024007Y4</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO68</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1405,27 +1405,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>LF0024007Y4</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBCXPLFIO68</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1448,7 +1444,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1456,7 +1452,11 @@
           <t>BRBCXPLFIO76</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1466,25 +1466,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LF002400KBT</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>46234</v>
+        <v>46104</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO76</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LF002400KBU</t>
+          <t>LF002400KBT</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LF002400KBW</t>
+          <t>LF002400KBU</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LF002400KBX</t>
+          <t>LF002400KBW</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LF002400KBY</t>
+          <t>LF002400KBX</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBY</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1673,11 +1673,7 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1692,7 +1688,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -1700,7 +1696,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1710,7 +1706,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>567798-LF0</t>
+          <t>567797-LF0</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1723,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -1735,7 +1731,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1743,35 +1739,39 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>45582</v>
+        <v>46234</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45454</v>
+        <v>45582</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2006,20 +2006,20 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45455</v>
+        <v>45454</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2099,20 +2099,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45461</v>
+        <v>45455</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2161,11 +2161,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45462</v>
+        <v>45461</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -2192,20 +2192,20 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45464</v>
+        <v>45462</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2249,16 +2249,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45582</v>
+        <v>45464</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2275,28 +2275,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>46181</v>
+        <v>45582</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>FIRF GERAES 30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>BRABCBLFIM30</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -2307,25 +2311,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>46237</v>
+        <v>46181</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BRBBDCLTR2X9</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2351,7 +2355,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2359,11 +2363,7 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -2386,15 +2386,19 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2404,25 +2408,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -2448,7 +2452,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2479,7 +2483,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2487,11 +2491,7 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2501,28 +2501,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>45929</v>
+        <v>46251</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2532,16 +2536,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46332</v>
+        <v>45929</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2550,7 +2554,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -2568,11 +2572,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>46395</v>
+        <v>46332</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2581,7 +2585,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2594,25 +2598,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>46486</v>
+        <v>46395</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2638,7 +2642,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2646,11 +2650,7 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2681,7 +2681,11 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2696,20 +2700,20 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2735,7 +2739,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2766,7 +2770,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2797,7 +2801,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2805,11 +2809,7 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2840,7 +2840,11 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2850,25 +2854,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -2894,7 +2898,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2925,7 +2929,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2956,7 +2960,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2979,20 +2983,20 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -3018,7 +3022,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3036,98 +3040,86 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>47343</v>
+        <v>46199</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>BRBSAFLFNG47</t>
-        </is>
-      </c>
+          <t>CARMEL INFRA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>46454</v>
+        <v>46199</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>46454</v>
+        <v>47343</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3150,7 +3142,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3160,7 +3152,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3172,30 +3164,30 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3207,25 +3199,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3242,30 +3234,30 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>47217</v>
+        <v>46083</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3277,16 +3269,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>47217</v>
+        <v>46083</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3295,12 +3287,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3309,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LFSC19002HS</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
@@ -3330,10 +3322,80 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LFSC19002HS</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -3056,7 +3056,11 @@
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2373,27 +2373,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>46237</v>
+        <v>46181</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2417,7 +2413,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2425,11 +2421,7 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2444,7 +2436,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
@@ -2452,15 +2444,19 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2470,25 +2466,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -2514,7 +2510,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2545,7 +2541,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2553,11 +2549,7 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2567,28 +2559,32 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>45929</v>
+        <v>46251</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2598,16 +2594,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>46332</v>
+        <v>45929</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2616,7 +2612,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2634,11 +2630,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>46395</v>
+        <v>46332</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2647,7 +2643,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2660,25 +2656,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>46486</v>
+        <v>46395</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2704,7 +2700,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2712,11 +2708,7 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2731,7 +2723,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
@@ -2739,7 +2731,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2747,7 +2739,11 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2762,20 +2758,20 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -2793,20 +2789,20 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -2832,7 +2828,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2863,7 +2859,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2871,11 +2867,7 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2890,7 +2882,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
@@ -2898,7 +2890,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2916,28 +2908,32 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+          <t>BRBPACLFIWC2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2947,25 +2943,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -2991,7 +2987,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3022,7 +3018,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3045,22 +3041,18 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>BRBMGBLFI6I3</t>
-        </is>
-      </c>
+          <t>CARMEL INFRA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3076,20 +3068,20 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3107,11 +3099,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3120,7 +3112,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -3133,25 +3125,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>47343</v>
+        <v>46199</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -3159,107 +3151,95 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>46454</v>
+        <v>46199</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>46454</v>
+        <v>46199</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBMGBLFI6I3</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>46454</v>
+        <v>47343</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3269,16 +3249,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3287,7 +3267,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3304,16 +3284,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3322,7 +3302,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3339,30 +3319,30 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>47217</v>
+        <v>46454</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3374,30 +3354,30 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>47217</v>
+        <v>46083</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3409,28 +3389,133 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>BANCO XP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LF00240072E</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>BRBCXPLFIKS5</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>BANCO BMG S.A.</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>LFSC19002CD</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7Q4</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>609712-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>LFSC19002CE</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>LFSC19002HS</t>
         </is>
       </c>
-      <c r="D94" s="2" t="n">
+      <c r="D97" s="2" t="n">
         <v>47217</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>JERA2026</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F97" t="inlineStr">
         <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2400,27 +2400,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2444,7 +2440,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2452,11 +2448,7 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2471,7 +2463,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
@@ -2479,15 +2471,19 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2497,25 +2493,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2541,7 +2537,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2572,7 +2568,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2580,11 +2576,7 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2594,28 +2586,32 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>45929</v>
+        <v>46251</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2625,16 +2621,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>46332</v>
+        <v>45929</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2643,7 +2639,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2661,11 +2657,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>46395</v>
+        <v>46332</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2674,7 +2670,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2687,25 +2683,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>46486</v>
+        <v>46395</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2731,7 +2727,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2739,11 +2735,7 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2758,7 +2750,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
@@ -2766,7 +2758,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2774,7 +2766,11 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2797,7 +2793,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2820,20 +2816,20 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -2859,7 +2855,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2890,7 +2886,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2921,7 +2917,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2929,11 +2925,7 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2948,7 +2940,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
@@ -2956,7 +2948,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2964,7 +2956,11 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2974,25 +2970,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -3018,7 +3014,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3049,10 +3045,14 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
+          <t>BORDEAUX INFRA</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
@@ -3076,14 +3076,10 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
+          <t>CARMEL INFRA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3107,7 +3103,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3130,20 +3126,20 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -3169,7 +3165,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3200,7 +3196,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3218,25 +3214,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>47343</v>
+        <v>46199</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -3244,37 +3240,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>46454</v>
+        <v>47343</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3297,7 +3289,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3307,7 +3299,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3324,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3354,30 +3346,30 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3394,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3412,7 +3404,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3424,16 +3416,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>47217</v>
+        <v>46083</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3442,12 +3434,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3456,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
@@ -3477,12 +3469,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3491,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LFSC19002HS</t>
+          <t>LFSC19002CE</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
@@ -3512,10 +3504,45 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LFSC19002HS</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,27 +539,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>CDB3239C4TL</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>46454</v>
+        <v>46223</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
+          <t>FIRF GERAES</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -583,7 +579,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -614,7 +610,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -645,7 +641,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -676,7 +672,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -707,7 +703,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -725,25 +721,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PARANA BANCO S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CDB3253PPYA</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>46091</v>
+        <v>46454</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>BRPRBCC059P8</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -769,7 +765,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -800,7 +796,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -831,7 +827,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -839,11 +835,7 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -866,7 +858,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -874,7 +866,11 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -897,7 +893,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -905,11 +901,7 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -919,28 +911,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>PARANA BANCO S.A.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CDB424EERW3</t>
+          <t>CDB3253PPYA</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>46146</v>
+        <v>46091</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>BRBVKWC00WA0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>BRPRBCC059P8</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -963,7 +959,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BBRASIL FIM</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -981,32 +977,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BANCO INTER SA</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CDB7257QUDF</t>
+          <t>CDB424EERW3</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>46213</v>
+        <v>46146</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>BBRASIL FIM</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>BRBIDIC002H4</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>613312-CDB</t>
-        </is>
-      </c>
+          <t>BRBVKWC00WA0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1021,7 +1013,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CDB7257QUDG</t>
+          <t>CDB7257QUDF</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1029,7 +1021,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1037,7 +1029,11 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>613312-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1052,7 +1048,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CDB7257QUDH</t>
+          <t>CDB7257QUDG</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1060,7 +1056,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1083,7 +1079,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CDB7257QUDI</t>
+          <t>CDB7257QUDH</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1091,7 +1087,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1099,11 +1095,7 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>613315-CDB</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1113,56 +1105,60 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>BANCO INTER SA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CDB925CDN0L</t>
+          <t>CDB7257QUDI</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>46013</v>
+        <v>46213</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>BRBVKWC01543</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>BRBIDIC002H4</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>613315-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB925CDN0L</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>46213</v>
+        <v>46013</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
+          <t>BRBVKWC01543</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -1188,7 +1184,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1196,11 +1192,7 @@
           <t>BRHAPVDBS014</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>362409-HAP</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1210,28 +1202,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>47196</v>
+        <v>46213</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>BRHAPVDBS014</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>362409-HAP</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1254,7 +1250,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1285,7 +1281,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1316,7 +1312,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1347,7 +1343,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1355,42 +1351,42 @@
           <t>BRKLBNDBS004</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>353017-KLB</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>46083</v>
+        <v>47196</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>353017-KLB</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1405,20 +1401,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LF0024007Y4</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO68</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1436,27 +1432,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>LF0024007Y4</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBCXPLFIO68</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1471,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1487,7 +1479,11 @@
           <t>BRBCXPLFIO76</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1497,25 +1493,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LF002400KBT</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>46234</v>
+        <v>46104</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO76</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1533,7 +1529,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LF002400KBU</t>
+          <t>LF002400KBT</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
@@ -1541,7 +1537,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1564,7 +1560,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LF002400KBW</t>
+          <t>LF002400KBU</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -1595,7 +1591,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LF002400KBX</t>
+          <t>LF002400KBW</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -1603,7 +1599,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1626,7 +1622,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LF002400KBY</t>
+          <t>LF002400KBX</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -1634,7 +1630,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1657,7 +1653,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBY</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -1665,7 +1661,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1696,7 +1692,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1704,11 +1700,7 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1723,7 +1715,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
@@ -1731,7 +1723,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1741,7 +1733,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>567798-LF0</t>
+          <t>567797-LF0</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1750,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -1766,7 +1758,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1774,35 +1766,39 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>45582</v>
+        <v>46234</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -1820,7 +1816,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
@@ -1828,7 +1824,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1851,7 +1847,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -1859,7 +1855,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1877,25 +1873,25 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45454</v>
+        <v>45582</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -1913,7 +1909,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -1921,12 +1917,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -1952,7 +1948,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1983,7 +1979,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2014,7 +2010,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2037,20 +2033,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45455</v>
+        <v>45454</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2076,7 +2072,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2099,7 +2095,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
@@ -2112,7 +2108,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -2130,20 +2126,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45461</v>
+        <v>45455</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2169,7 +2165,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2192,11 +2188,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45462</v>
+        <v>45461</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2205,7 +2201,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -2223,20 +2219,20 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45464</v>
+        <v>45462</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -2262,7 +2258,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2280,16 +2276,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45582</v>
+        <v>45464</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2298,7 +2294,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -2306,30 +2302,30 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>46181</v>
+        <v>45582</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRABCBLFIM30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2351,7 +2347,7 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2382,14 +2378,18 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>46181</v>
+        <v>46240</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>BH INFRA</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2427,27 +2427,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2471,7 +2467,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2479,11 +2475,7 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2498,7 +2490,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -2506,15 +2498,19 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2524,25 +2520,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -2568,7 +2564,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2599,7 +2595,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2607,11 +2603,7 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2621,28 +2613,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>45929</v>
+        <v>46251</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2652,16 +2648,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>46332</v>
+        <v>45929</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2670,7 +2666,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2688,11 +2684,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>46395</v>
+        <v>46332</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2701,7 +2697,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2714,25 +2710,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>46486</v>
+        <v>46395</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -2758,7 +2754,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2766,11 +2762,7 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2785,7 +2777,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
@@ -2793,7 +2785,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2801,7 +2793,11 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2824,7 +2820,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2847,20 +2843,20 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -2886,7 +2882,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2917,7 +2913,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2948,7 +2944,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2956,11 +2952,7 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2975,7 +2967,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -2983,7 +2975,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2991,7 +2983,11 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3001,25 +2997,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -3045,7 +3041,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3076,10 +3072,14 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>BORDEAUX INFRA</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
@@ -3103,14 +3103,10 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
+          <t>CARMEL INFRA</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -3134,7 +3130,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3157,20 +3153,20 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -3196,7 +3192,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3227,7 +3223,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3245,25 +3241,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>47343</v>
+        <v>46199</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -3271,37 +3267,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>46454</v>
+        <v>47343</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3324,7 +3316,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3334,7 +3326,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3351,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3381,30 +3373,30 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3429,7 +3421,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3439,7 +3431,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3451,16 +3443,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>47217</v>
+        <v>46083</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3469,12 +3461,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3483,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
@@ -3504,12 +3496,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
     </row>
@@ -3526,7 +3518,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LFSC19002HS</t>
+          <t>LFSC19002CE</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
@@ -3539,10 +3531,45 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LFSC19002HS</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>

--- a/Dados/ativos_mapeados_para_controle.xlsx
+++ b/Dados/ativos_mapeados_para_controle.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,7 +738,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -756,25 +756,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PARANA BANCO S.A.</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CDB3253PPYA</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>46091</v>
+        <v>46454</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>BRPRBCC059P8</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -800,7 +800,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -870,11 +870,7 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -897,7 +893,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -905,7 +901,11 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -936,11 +936,7 @@
           <t>BRPRBCC059P8</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>606488-CDB</t>
-        </is>
-      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -950,28 +946,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>PARANA BANCO S.A.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CDB424EERW3</t>
+          <t>CDB3253PPYA</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>46146</v>
+        <v>46091</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>BRBVKWC00WA0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>BRPRBCC059P8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>606488-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>BBRASIL FIM</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1012,32 +1012,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BANCO INTER SA</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CDB7257QUDF</t>
+          <t>CDB424EERW3</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>46213</v>
+        <v>46146</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>BBRASIL FIM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BRBIDIC002H4</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>613312-CDB</t>
-        </is>
-      </c>
+          <t>BRBVKWC00WA0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1052,7 +1048,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CDB7257QUDG</t>
+          <t>CDB7257QUDF</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1060,7 +1056,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1068,7 +1064,11 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>613312-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CDB7257QUDH</t>
+          <t>CDB7257QUDG</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CDB7257QUDI</t>
+          <t>CDB7257QUDH</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1130,11 +1130,7 @@
           <t>BRBIDIC002H4</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>613315-CDB</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1144,56 +1140,60 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BANCO VOLKSWAGEN S/A</t>
+          <t>BANCO INTER SA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CDB925CDN0L</t>
+          <t>CDB7257QUDI</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>46013</v>
+        <v>46213</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BBRASIL FIM CP RESP</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BRBVKWC01543</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>BRBIDIC002H4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>613315-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Debêntures</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
+          <t>BANCO VOLKSWAGEN S/A</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HAPV21</t>
+          <t>CDB925CDN0L</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>46213</v>
+        <v>46013</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BBRASIL FIM CP RESP</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BRHAPVDBS014</t>
+          <t>BRBVKWC01543</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1227,11 +1227,7 @@
           <t>BRHAPVDBS014</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>362409-HAP</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1241,28 +1237,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KLABIN S/A</t>
+          <t>HAPVIDA PARTICIPACOES E INVESTIMENTOS S/A</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KLBNA2</t>
+          <t>HAPV21</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>47196</v>
+        <v>46213</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BRKLBNDBS004</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>BRHAPVDBS014</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>362409-HAP</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1386,42 +1386,42 @@
           <t>BRKLBNDBS004</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>353017-KLB</t>
-        </is>
-      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Letra Financeira</t>
+          <t>Debêntures</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>KLABIN S/A</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>KLBNA2</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>46083</v>
+        <v>47196</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>BRKLBNDBS004</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>353017-KLB</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1436,20 +1436,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LF0024007Y4</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO68</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1467,27 +1467,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LF0024008OB</t>
+          <t>LF0024007Y4</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>46104</v>
+        <v>46097</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BRBCXPLFIO76</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBCXPLFIO68</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1510,7 +1506,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1518,7 +1514,11 @@
           <t>BRBCXPLFIO76</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>614522-CDB</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1528,25 +1528,25 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LF002400KBT</t>
+          <t>LF0024008OB</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>46234</v>
+        <v>46104</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BRBMEBLFI8V4</t>
+          <t>BRBCXPLFIO76</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LF002400KBU</t>
+          <t>LF002400KBT</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LF002400KBW</t>
+          <t>LF002400KBU</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LF002400KBX</t>
+          <t>LF002400KBW</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LF002400KBY</t>
+          <t>LF002400KBX</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LF002400KC0</t>
+          <t>LF002400KBY</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1735,11 +1735,7 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>567797-LF0</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1754,7 +1750,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LF002400KC1</t>
+          <t>LF002400KC0</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -1762,7 +1758,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1772,7 +1768,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>567798-LF0</t>
+          <t>567797-LF0</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1785,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LF002400KC2</t>
+          <t>LF002400KC1</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TOPAZIO INFRA</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1805,35 +1801,39 @@
           <t>BRBMEBLFI8V4</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>567798-LF0</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LFSC</t>
+          <t>Letra Financeira</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO MERCANTIL DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LFSC19003FD</t>
+          <t>LF002400KC2</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45582</v>
+        <v>46234</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>TOPAZIO INFRA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BRABCBLFN7I2</t>
+          <t>BRBMEBLFI8V4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LFSC19003W3</t>
+          <t>LFSC19003FD</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LFSC19003W4</t>
+          <t>LFSC19003W3</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1908,25 +1908,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LFSC190054C</t>
+          <t>LFSC19003W4</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45454</v>
+        <v>45582</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BRBNBRLFI013</t>
+          <t>BRABCBLFN7I2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LFSC190054D</t>
+          <t>LFSC190054C</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BRBNBRLFI021</t>
+          <t>BRBNBRLFI013</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2068,20 +2068,20 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LFSC190054I</t>
+          <t>LFSC190054D</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45455</v>
+        <v>45454</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>BRBNBRLFI039</t>
+          <t>BRBNBRLFI021</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LFSC190059S</t>
+          <t>LFSC190054I</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BRBNBRLFI062</t>
+          <t>BRBNBRLFI039</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2161,20 +2161,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LFSC19005FF</t>
+          <t>LFSC190059S</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45461</v>
+        <v>45455</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0C5</t>
+          <t>BRBNBRLFI062</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2223,11 +2223,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LFSC19005L1</t>
+          <t>LFSC19005FF</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45462</v>
+        <v>45461</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0F8</t>
+          <t>BRBNBRLFI0C5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -2254,20 +2254,20 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LFSC19005L3</t>
+          <t>LFSC19005L1</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45464</v>
+        <v>45462</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>BRBNBRLFI0G6</t>
+          <t>BRBNBRLFI0F8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2311,16 +2311,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO DO NORDESTE DO BRASIL S.A.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>LFSC19007G2</t>
+          <t>LFSC19005L3</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45582</v>
+        <v>45464</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>BRABCBLFIM30</t>
+          <t>BRBNBRLFI0G6</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -2337,30 +2337,30 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LFSN</t>
+          <t>LFSC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LFSN1800D4W</t>
+          <t>LFSC19007G2</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>46181</v>
+        <v>45582</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>BRBSAFLNND73</t>
+          <t>BRABCBLFIM30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2413,14 +2413,18 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>46181</v>
+        <v>46240</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>BH INFRA</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>BRBSAFLNND73</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2440,7 +2444,7 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>46240</v>
+        <v>46181</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2458,27 +2462,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BANCO BRADESCO S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LFSN1800DG1</t>
+          <t>LFSN1800D4W</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>CARMEL INFRA</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>BRBBDCLTR2X9</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2510,11 +2510,7 @@
           <t>BRBBDCLTR2X9</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>407137-LFS</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2529,7 +2525,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LFSN1800DIG</t>
+          <t>LFSN1800DG1</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
@@ -2537,15 +2533,19 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>BRBBDCLTROH4</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
+          <t>BRBBDCLTR2X9</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>407137-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2555,25 +2555,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BRADESCO S.A.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LFSN1800DS5</t>
+          <t>LFSN1800DIG</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>BRBSAFLNN8B3</t>
+          <t>BRBBDCLTROH4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BORDEAUX INFRA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2638,11 +2638,7 @@
           <t>BRBSAFLNN8B3</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>335769-LFS</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2652,28 +2648,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BANCO ABC BRASIL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LFSN1800E2G</t>
+          <t>LFSN1800DS5</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>45929</v>
+        <v>46251</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>BRABCBLFIM22</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
+          <t>BRBSAFLNN8B3</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>335769-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2683,16 +2683,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO ABC BRASIL S.A.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LFSN1800HXO</t>
+          <t>LFSN1800E2G</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>46332</v>
+        <v>45929</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>BRBSAFLNN7R1</t>
+          <t>BRABCBLFIM22</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2719,11 +2719,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LFSN1900008</t>
+          <t>LFSN1800HXO</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>46395</v>
+        <v>46332</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>BRBSAFLFNBB5</t>
+          <t>BRBSAFLNN7R1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -2745,25 +2745,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BANCO BTG PACTUAL S.A.</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LFSN19001BC</t>
+          <t>LFSN1900008</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>46486</v>
+        <v>46395</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>BRBPACLFIVQ4</t>
+          <t>BRBSAFLFNBB5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2797,11 +2797,7 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>353997-N L</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2816,7 +2812,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LFSN19001BH</t>
+          <t>LFSN19001BC</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
@@ -2824,7 +2820,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2832,7 +2828,11 @@
           <t>BRBPACLFIVQ4</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>353997-N L</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2878,20 +2878,20 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LFSN19006KM</t>
+          <t>LFSN19001BH</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>46904</v>
+        <v>46486</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>BRBPACLFIWC2</t>
+          <t>BRBPACLFIVQ4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HORIZONTE FIM</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MANACA INFRA</t>
+          <t>HORIZONTE FIM</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>MANACA INFRA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2987,11 +2987,7 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>513453-LFS</t>
-        </is>
-      </c>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3006,7 +3002,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LFSN19006KN</t>
+          <t>LFSN19006KM</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
@@ -3014,7 +3010,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3022,7 +3018,11 @@
           <t>BRBPACLFIWC2</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>513453-LFS</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3032,25 +3032,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO BTG PACTUAL S.A.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LFSN1900971</t>
+          <t>LFSN19006KN</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>46195</v>
+        <v>46904</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>BRBMGBLFI489</t>
+          <t>BRBPACLFIWC2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>BORDEAUX INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3107,10 +3107,14 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
+          <t>BORDEAUX INFRA</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>BRBMGBLFI489</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr"/>
     </row>
     <row r="86">
@@ -3134,14 +3138,10 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>BRBMGBLFI489</t>
-        </is>
-      </c>
+          <t>CARMEL INFRA</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
     </row>
     <row r="87">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3188,20 +3188,20 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LFSN19009YU</t>
+          <t>LFSN1900971</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>BH INFRA</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>BRBMGBLFI6I3</t>
+          <t>BRBMGBLFI489</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CARMEL INFRA</t>
+          <t>BH INFRA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>FIRF GERAES</t>
+          <t>CARMEL INFRA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3276,25 +3276,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BANCO SAFRA S.A.</t>
+          <t>BANCO BMG S.A.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LFSN1900CR5</t>
+          <t>LFSN19009YU</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>47343</v>
+        <v>46199</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>FIRF GERAES 30</t>
+          <t>FIRF GERAES</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BRBSAFLFNG47</t>
+          <t>BRBMGBLFI6I3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -3302,37 +3302,33 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Títulos Privados</t>
+          <t>LFSN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>AGIBANK</t>
+          <t>BANCO SAFRA S.A.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CDB3251WXH0</t>
+          <t>LFSN1900CR5</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>46454</v>
+        <v>47343</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>FIRF GERAES 30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>BRAGBKC00M66</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>614522-CDB</t>
-        </is>
-      </c>
+          <t>BRBSAFLFNG47</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3355,7 +3351,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3365,7 +3361,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3386,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>REAL FIM</t>
+          <t>JERA2026</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3412,30 +3408,30 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BANCO XP</t>
+          <t>AGIBANK</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LF00240072E</t>
+          <t>CDB3251WXH0</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>46083</v>
+        <v>46454</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>BMG SEG</t>
+          <t>REAL FIM</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BRBCXPLFIKS5</t>
+          <t>BRAGBKC00M66</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>614522-CDB</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3456,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>JERA2026</t>
+          <t>BMG SEG</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3470,7 +3466,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>353997-N L</t>
+          <t>614522-CDB</t>
         </is>
       </c>
     </row>
@@ -3482,16 +3478,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BANCO BMG S.A.</t>
+          <t>BANCO XP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LFSC19002CD</t>
+          <t>LF00240072E</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>47217</v>
+        <v>46083</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3500,12 +3496,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7Q4</t>
+          <t>BRBCXPLFIKS5</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>609712-LFS</t>
+          <t>353997-N L</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3518,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LFSC19002CE</t>
+          <t>LFSC19002CD</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
@@ -3535,12 +3531,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BRBMGBLFI7P6</t>
+          <t>BRBMGBLFI7Q4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>609711-LFS</t>
+          <t>609712-LFS</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3553,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LFSC19002HS</t>
+          <t>LFSC19002CE</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
@@ -3570,10 +3566,45 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
+          <t>BRBMGBLFI7P6</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>609711-LFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Títulos Privados</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>BANCO BMG S.A.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LFSC19002HS</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>47217</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>JERA2026</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
           <t>BRBMGBLFI7R2</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>609713-LFS</t>
         </is>
